--- a/data/tags/אלבומים חדשים/global/2026-03-week01/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-03-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ג'ייקוב אלון In Limerence</v>
+        <v>הארי סטיילס Kiss All The Time. Disco Occasionally</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%99%d7%99%d7%a7%d7%95%d7%91-%d7%90%d7%9c%d7%95%d7%9f-in-limerence/</v>
+        <v>https://yosmusic.com/%d7%94%d7%90%d7%a8%d7%99-%d7%a1%d7%98%d7%99%d7%99%d7%9c%d7%a1-kiss-all-the-time-disco-occasionally/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מדי פעם מופיע קול חדש עם השילוב האלכימי של יופי שברירי ופואטיות – כזה שיש לו את הכוח לגרום לזמן להיראות כאילו עצר מלכת. זהו אותו קסם שהפך את עמודי התווך של המוזיקה האלטרנטיבית, ג׳ף באקלי ולורה מרלינג, למה שהם,</v>
+        <v>מאז האלבום האחרון של הארי סטיילס, “Harry’s House” מ-2022, כוכב הפופ עשה כמה שינויים בחייו. האלבום ההוא יצא בתקופה של רכילות והשערות בלתי פוסקות סביב חייו האישיים, ובשנים שעברו מאז הוא ניסה להשיב לעצמו שליטה על הפרטיות שלו, כשהוא מנצל</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ג'ייקוב אלון In Limerence</v>
+        <v>הארי סטיילס Kiss All The Time. Disco Occasionally</v>
       </c>
     </row>
   </sheetData>
